--- a/GRÁFICAS.xlsx
+++ b/GRÁFICAS.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb4d9ba34e02ff95/Escritorio/US/3º/2º CUATRIMESTRE/ASD/TRABAJO-ASD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{224F6AC1-D5D9-4E39-93DA-166DED78EC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="8_{224F6AC1-D5D9-4E39-93DA-166DED78EC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{953D6FA2-5A3F-4DAD-8FCD-F80F0FCC5AEE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{7F44F516-FBB9-4CC1-AFE1-16562D403CA9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7F44F516-FBB9-4CC1-AFE1-16562D403CA9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
+    <sheet name="Tiempo vs tamaño de la matriz" sheetId="1" r:id="rId1"/>
+    <sheet name="Mejora distintas optimizacione " sheetId="5" r:id="rId2"/>
+    <sheet name="Tiempo vs número de hilos" sheetId="2" r:id="rId3"/>
+    <sheet name="Speedup (aceleración)" sheetId="3" r:id="rId4"/>
+    <sheet name="Eficiencia" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
   <si>
     <t>Nº de celdas</t>
   </si>
@@ -69,12 +71,42 @@
   <si>
     <t>Hilos</t>
   </si>
+  <si>
+    <t>Tiempo medio (No Optimizado)</t>
+  </si>
+  <si>
+    <t>NO OPTIMIZADO</t>
+  </si>
+  <si>
+    <t>OPTIMIZADO</t>
+  </si>
+  <si>
+    <t>Tiempo medio (Optimizado)</t>
+  </si>
+  <si>
+    <t>OPTIMIZADO (OPENMP+DESENRROLLADO)</t>
+  </si>
+  <si>
+    <t>OPTIMIZADO (OPENMP+DESENRROLLADO+MPI)</t>
+  </si>
+  <si>
+    <t>Tamaño celda</t>
+  </si>
+  <si>
+    <t>1000x1000</t>
+  </si>
+  <si>
+    <t>Tipo de código</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,6 +123,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -143,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -153,6 +193,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -191,12 +241,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -223,12 +270,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx2"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -242,39 +286,49 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
             <c:numRef>
-              <c:f>Hoja1!$D$12:$D$16</c:f>
+              <c:f>'Tiempo vs tamaño de la matriz'!$D$20:$D$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -295,35 +349,124 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Hoja1!$E$12:$E$16</c:f>
+              <c:f>'Tiempo vs tamaño de la matriz'!$E$20:$E$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.4521346666666668</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.0433236666666668</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.640733999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>72.271221333333344</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100.10557033333333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-ED29-4388-92C9-6ED2AE68496D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Tiempo vs tamaño de la matriz'!$D$20:$D$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.24781233333333333</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0187926666666667</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.9055646666666668</c:v>
+                  <c:v>160000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.2509146666666666</c:v>
+                  <c:v>640000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.494664666666665</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Tiempo vs tamaño de la matriz'!$F$20:$F$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-ED29-4388-92C9-6ED2AE68496D}"/>
+              <c16:uniqueId val="{00000000-3201-4C05-808E-341F76634308}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -335,10 +478,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="1600536591"/>
         <c:axId val="1600527951"/>
-      </c:scatterChart>
-      <c:valAx>
+      </c:barChart>
+      <c:catAx>
         <c:axId val="1600536591"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -349,7 +493,7 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:schemeClr val="tx2">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
@@ -359,20 +503,73 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-ES"/>
+                  <a:t>Número</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="es-ES" baseline="0"/>
+                  <a:t> de celdas</a:t>
+                </a:r>
+                <a:endParaRPr lang="es-ES"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln>
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -383,10 +580,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -398,8 +592,11 @@
         </c:txPr>
         <c:crossAx val="1600527951"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
       <c:valAx>
         <c:axId val="1600527951"/>
         <c:scaling>
@@ -411,7 +608,7 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:schemeClr val="tx2">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
@@ -421,20 +618,68 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-ES"/>
+                  <a:t>Tiempo</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln>
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -445,10 +690,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -460,7 +702,7 @@
         </c:txPr>
         <c:crossAx val="1600536591"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -480,7 +722,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="tx2">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -612,7 +854,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Hoja2!$B$4:$B$8</c:f>
+              <c:f>'Tiempo vs número de hilos'!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -636,24 +878,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Hoja2!$F$4:$F$8</c:f>
+              <c:f>'Tiempo vs número de hilos'!$F$4:$F$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -926,6 +1168,485 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1441,536 +2162,20 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>617220</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1993,6 +2198,72 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>655320</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="CuadroTexto 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38AF1989-AD0A-C5DC-DC29-E0F481A48833}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9037320" y="3653790"/>
+          <a:ext cx="3985260" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1100"/>
+            <a:t>TODAS LAS MEDICIONES</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1100" baseline="0"/>
+            <a:t> REALIZADAS SE LLEVAN A CABO EN MODO BENCHMARK, ES DECIR, TENEMOS SOLO EN CUENTA CUANTO TARDA EL ALGORITMO, DEJANDO DE LADO EL TIEMPO DE IMPRESIÓN POR PANTALLA DE LOS ELEMENTOS.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2037,6 +2308,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2356,16 +2631,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B534E41D-3C7D-4DEA-BD8A-972D6BFF01A7}">
-  <dimension ref="B3:G16"/>
+  <dimension ref="B2:G24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" customWidth="1"/>
     <col min="4" max="4" width="14.88671875" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.5546875" customWidth="1"/>
+    <col min="6" max="6" width="24.109375" customWidth="1"/>
+    <col min="7" max="7" width="25.21875" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -2387,164 +2674,291 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="1">
+      <c r="B4" s="6">
         <v>100</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="6">
         <v>100</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1.6113980000000001</v>
+      </c>
+      <c r="F4" s="7">
+        <v>1.4158440000000001</v>
+      </c>
+      <c r="G4" s="7">
+        <v>1.329162</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="6">
+        <v>200</v>
+      </c>
+      <c r="C5" s="6">
+        <v>200</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E5" s="7">
+        <v>5.0053109999999998</v>
+      </c>
+      <c r="F5" s="7">
+        <v>4.5624589999999996</v>
+      </c>
+      <c r="G5" s="7">
+        <v>5.562201</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="6">
+        <v>400</v>
+      </c>
+      <c r="C6" s="6">
+        <v>400</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E6" s="7">
+        <v>19.26736</v>
+      </c>
+      <c r="F6" s="7">
+        <v>18.937560000000001</v>
+      </c>
+      <c r="G6" s="7">
+        <v>17.717282000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="6">
+        <v>800</v>
+      </c>
+      <c r="C7" s="6">
+        <v>800</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="7">
+        <v>71.624598000000006</v>
+      </c>
+      <c r="F7" s="7">
+        <v>72.698080000000004</v>
+      </c>
+      <c r="G7" s="7">
+        <v>72.490986000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="6">
+        <v>1000</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1000</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="7">
+        <v>101.41100900000001</v>
+      </c>
+      <c r="F8" s="7">
+        <v>100.48173800000001</v>
+      </c>
+      <c r="G8" s="7">
+        <v>98.423963999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="6">
         <v>100</v>
       </c>
-      <c r="E4" s="1">
-        <v>0.26460299999999998</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.22483800000000001</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.253996</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="1">
+      <c r="C12" s="6">
+        <v>100</v>
+      </c>
+      <c r="D12" s="6">
+        <v>100</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="6">
         <v>200</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C13" s="6">
         <v>200</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D13" s="6">
         <v>100</v>
       </c>
-      <c r="E5" s="1">
-        <v>1.067401</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0.98209500000000005</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.0068820000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="1">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="6">
         <v>400</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C14" s="6">
         <v>400</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D14" s="6">
         <v>100</v>
       </c>
-      <c r="E6" s="1">
-        <v>3.5067940000000002</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2.4811269999999999</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2.7287729999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="1">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="6">
         <v>800</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C15" s="6">
         <v>800</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D15" s="6">
         <v>100</v>
       </c>
-      <c r="E7" s="1">
-        <v>9.2833690000000004</v>
-      </c>
-      <c r="F7" s="1">
-        <v>7.6164170000000002</v>
-      </c>
-      <c r="G7" s="1">
-        <v>7.8529580000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="1">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="6">
         <v>1000</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C16" s="6">
         <v>1000</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D16" s="6">
         <v>100</v>
       </c>
-      <c r="E8" s="1">
-        <v>12.838881000000001</v>
-      </c>
-      <c r="F8" s="1">
-        <v>11.433185999999999</v>
-      </c>
-      <c r="G8" s="1">
-        <v>10.211926999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="2" t="s">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D19" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="1">
+      <c r="E19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D20" s="6">
         <f>B4*C4</f>
         <v>10000</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E20" s="7">
         <f>AVERAGE(E4:G4)</f>
-        <v>0.24781233333333333</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="1">
+        <v>1.4521346666666668</v>
+      </c>
+      <c r="F20" s="7" t="e">
+        <f>AVERAGE(E12:G12)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D21" s="6">
         <f>B5*C5</f>
         <v>40000</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E21" s="7">
         <f>AVERAGE(E5:G5)</f>
-        <v>1.0187926666666667</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D14" s="1">
+        <v>5.0433236666666668</v>
+      </c>
+      <c r="F21" s="7" t="e">
+        <f t="shared" ref="F21:F24" si="0">AVERAGE(E13:G13)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D22" s="6">
         <f>B6*C6</f>
         <v>160000</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E22" s="7">
         <f>AVERAGE(E6:G6)</f>
-        <v>2.9055646666666668</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="1">
+        <v>18.640733999999998</v>
+      </c>
+      <c r="F22" s="7" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D23" s="6">
         <f>B7*C7</f>
         <v>640000</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E23" s="7">
         <f>AVERAGE(E7:G7)</f>
-        <v>8.2509146666666666</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D16" s="1">
+        <v>72.271221333333344</v>
+      </c>
+      <c r="F23" s="7" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D24" s="6">
         <f>B8*C8</f>
         <v>1000000</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E24" s="7">
         <f>AVERAGE(E8:G8)</f>
-        <v>11.494664666666665</v>
+        <v>100.10557033333333</v>
+      </c>
+      <c r="F24" s="7" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B10:G10"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2552,6 +2966,104 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{525178EA-6457-4E02-8C1B-7AB9DF124C34}">
+  <dimension ref="B3:G7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="42.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E4" s="7">
+        <v>101.41100900000001</v>
+      </c>
+      <c r="F4" s="7">
+        <v>100.48173800000001</v>
+      </c>
+      <c r="G4" s="7">
+        <v>98.423963999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92881DEB-188C-4DB1-9AD4-F893FE6A3258}">
   <dimension ref="B3:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2582,90 +3094,60 @@
       <c r="B4" s="4">
         <v>1</v>
       </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="4">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="1" t="e">
         <f>AVERAGE(C4:E4)</f>
-        <v>2</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
         <v>2</v>
       </c>
-      <c r="C5" s="4">
-        <v>4</v>
-      </c>
-      <c r="D5" s="4">
-        <v>5</v>
-      </c>
-      <c r="E5" s="4">
-        <v>6</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="1" t="e">
         <f t="shared" ref="F5:F8" si="0">AVERAGE(C5:E5)</f>
-        <v>5</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="4">
         <v>4</v>
       </c>
-      <c r="C6" s="4">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4">
-        <v>8</v>
-      </c>
-      <c r="E6" s="4">
-        <v>9</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="1" t="e">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>8</v>
       </c>
-      <c r="C7" s="4">
-        <v>10</v>
-      </c>
-      <c r="D7" s="4">
-        <v>11</v>
-      </c>
-      <c r="E7" s="4">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="1" t="e">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>10</v>
       </c>
-      <c r="C8" s="4">
-        <v>13</v>
-      </c>
-      <c r="D8" s="4">
-        <v>14</v>
-      </c>
-      <c r="E8" s="4">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="1" t="e">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
@@ -2674,7 +3156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB542A8C-C0A9-4DEF-9353-02F1205ED9B2}">
   <dimension ref="B3:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2789,4 +3271,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D9DBD18-7035-4CD6-847F-50448158232D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/GRÁFICAS.xlsx
+++ b/GRÁFICAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb4d9ba34e02ff95/Escritorio/US/3º/2º CUATRIMESTRE/ASD/TRABAJO-ASD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="161" documentId="8_{224F6AC1-D5D9-4E39-93DA-166DED78EC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{953D6FA2-5A3F-4DAD-8FCD-F80F0FCC5AEE}"/>
+  <xr:revisionPtr revIDLastSave="197" documentId="8_{224F6AC1-D5D9-4E39-93DA-166DED78EC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F85AEECC-3A83-4D47-A878-0E4F4074ACE1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7F44F516-FBB9-4CC1-AFE1-16562D403CA9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7F44F516-FBB9-4CC1-AFE1-16562D403CA9}"/>
   </bookViews>
   <sheets>
     <sheet name="Tiempo vs tamaño de la matriz" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Nº de celdas</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>Tipo de código</t>
+  </si>
+  <si>
+    <t>OPTIMIZADO (OPENMP)</t>
   </si>
 </sst>
 </file>
@@ -193,9 +196,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -203,6 +203,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,13 +566,14 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx2">
                 <a:lumMod val="40000"/>
                 <a:lumOff val="60000"/>
               </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -750,6 +754,311 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Tiempo</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-ES" baseline="0"/>
+              <a:t> de ejecución en relación a la optimización del código</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Mejora distintas optimizacione '!$B$4:$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>NO OPTIMIZADO</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>OPTIMIZADO (OPENMP)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>OPTIMIZADO (OPENMP+DESENRROLLADO)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OPTIMIZADO (OPENMP+DESENRROLLADO+MPI)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Mejora distintas optimizacione '!$H$4:$H$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>100.10557033333333</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18.490322666666668</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.2544346666666666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3D2F-4679-A73F-7D092E9416D2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1318636527"/>
+        <c:axId val="1318637487"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1318636527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1318637487"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1318637487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1318636527"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -1167,6 +1476,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
   <cs:axisTitle>
@@ -1647,6 +1996,511 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2270,6 +3124,47 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1615440</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EBF9CED-AC19-F632-BA64-A863C866968B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2644,14 +3539,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
@@ -2674,114 +3569,114 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>100</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>100</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>1000</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>1.6113980000000001</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>1.4158440000000001</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>1.329162</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>200</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>200</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>1000</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>5.0053109999999998</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>4.5624589999999996</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>5.562201</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>400</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>400</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>1000</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>19.26736</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>18.937560000000001</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>17.717282000000001</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>800</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>800</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>1000</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>71.624598000000006</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>72.698080000000004</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>72.490986000000007</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>1000</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>1000</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>1000</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>101.41100900000001</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>100.48173800000001</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>98.423963999999998</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
@@ -2804,74 +3699,74 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>100</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>100</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>100</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>200</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>200</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>100</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>400</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>400</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>100</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>800</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>800</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>100</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>1000</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>1000</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>100</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="19" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D19" s="2" t="s">
@@ -2885,71 +3780,71 @@
       </c>
     </row>
     <row r="20" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <f>B4*C4</f>
         <v>10000</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="6">
         <f>AVERAGE(E4:G4)</f>
         <v>1.4521346666666668</v>
       </c>
-      <c r="F20" s="7" t="e">
+      <c r="F20" s="6" t="e">
         <f>AVERAGE(E12:G12)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="21" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <f>B5*C5</f>
         <v>40000</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="6">
         <f>AVERAGE(E5:G5)</f>
         <v>5.0433236666666668</v>
       </c>
-      <c r="F21" s="7" t="e">
+      <c r="F21" s="6" t="e">
         <f t="shared" ref="F21:F24" si="0">AVERAGE(E13:G13)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <f>B6*C6</f>
         <v>160000</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="6">
         <f>AVERAGE(E6:G6)</f>
         <v>18.640733999999998</v>
       </c>
-      <c r="F22" s="7" t="e">
+      <c r="F22" s="6" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <f>B7*C7</f>
         <v>640000</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="6">
         <f>AVERAGE(E7:G7)</f>
         <v>72.271221333333344</v>
       </c>
-      <c r="F23" s="7" t="e">
+      <c r="F23" s="6" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="24" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <f>B8*C8</f>
         <v>1000000</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="6">
         <f>AVERAGE(E8:G8)</f>
         <v>100.10557033333333</v>
       </c>
-      <c r="F24" s="7" t="e">
+      <c r="F24" s="6" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -2967,15 +3862,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{525178EA-6457-4E02-8C1B-7AB9DF124C34}">
-  <dimension ref="B3:G7"/>
+  <dimension ref="B3:H7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="42.5546875" customWidth="1"/>
     <col min="3" max="3" width="15.109375" customWidth="1"/>
     <col min="4" max="4" width="14.21875" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
@@ -2994,72 +3890,104 @@
       <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>1000</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>101.41100900000001</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>100.48173800000001</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>98.423963999999998</v>
       </c>
+      <c r="H4" s="6">
+        <f>AVERAGE(E4:G4)</f>
+        <v>100.10557033333333</v>
+      </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1000</v>
+      </c>
+      <c r="E5" s="6">
+        <v>18.777006</v>
+      </c>
+      <c r="F5" s="6">
+        <v>19.98086</v>
+      </c>
+      <c r="G5" s="6">
+        <v>16.713101999999999</v>
+      </c>
+      <c r="H5" s="6">
+        <f t="shared" ref="H5:H7" si="0">AVERAGE(E5:G5)</f>
+        <v>18.490322666666668</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D6" s="5">
         <v>1000</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="E6" s="6">
+        <v>7.7358529999999996</v>
+      </c>
+      <c r="F6" s="6">
+        <v>8.3516139999999996</v>
+      </c>
+      <c r="G6" s="6">
+        <v>8.6758369999999996</v>
+      </c>
+      <c r="H6" s="6">
+        <f t="shared" si="0"/>
+        <v>8.2544346666666666</v>
+      </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="6" t="s">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D7" s="5">
         <v>1000</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1000</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/GRÁFICAS.xlsx
+++ b/GRÁFICAS.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb4d9ba34e02ff95/Escritorio/US/3º/2º CUATRIMESTRE/ASD/TRABAJO-ASD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="197" documentId="8_{224F6AC1-D5D9-4E39-93DA-166DED78EC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F85AEECC-3A83-4D47-A878-0E4F4074ACE1}"/>
+  <xr:revisionPtr revIDLastSave="224" documentId="8_{224F6AC1-D5D9-4E39-93DA-166DED78EC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1AB9B91-5A40-4C3E-95CD-1EEC933B865B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7F44F516-FBB9-4CC1-AFE1-16562D403CA9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7F44F516-FBB9-4CC1-AFE1-16562D403CA9}"/>
   </bookViews>
   <sheets>
     <sheet name="Tiempo vs tamaño de la matriz" sheetId="1" r:id="rId1"/>
     <sheet name="Mejora distintas optimizacione " sheetId="5" r:id="rId2"/>
-    <sheet name="Tiempo vs número de hilos" sheetId="2" r:id="rId3"/>
-    <sheet name="Speedup (aceleración)" sheetId="3" r:id="rId4"/>
-    <sheet name="Eficiencia" sheetId="4" r:id="rId5"/>
+    <sheet name="Speedup (aceleración)" sheetId="3" r:id="rId3"/>
+    <sheet name="Eficiencia" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
   <si>
     <t>Nº de celdas</t>
   </si>
@@ -450,19 +449,19 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4.8563816666666666</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>4.8257756666666669</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>5.6524186666666667</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>9.9986663333333343</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>10.634561333333334</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -880,10 +879,10 @@
                   <c:v>18.490322666666668</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.2544346666666666</c:v>
+                  <c:v>15.680649000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>10.634561333333334</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1058,344 +1057,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
-              <a:t>Tiempo de ejecución en función del número de hilos</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-ES"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Tiempo vs número de hilos'!$B$4:$B$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>10</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Tiempo vs número de hilos'!$F$4:$F$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AA08-4E3D-AD45-B149B4A87CC8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1600535631"/>
-        <c:axId val="1600530351"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1600535631"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1600530351"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1600530351"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1600535631"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1476,46 +1137,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
   <cs:axisTitle>
@@ -2481,522 +2102,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -3144,47 +2249,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EBF9CED-AC19-F632-BA64-A863C866968B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>617220</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55440BA6-9604-CF9E-1D51-FF98652D9C38}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3706,11 +2770,17 @@
         <v>100</v>
       </c>
       <c r="D12" s="5">
-        <v>100</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+        <v>1000</v>
+      </c>
+      <c r="E12" s="5">
+        <v>4.8566950000000002</v>
+      </c>
+      <c r="F12" s="5">
+        <v>4.8558019999999997</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4.8566479999999999</v>
+      </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
@@ -3720,11 +2790,17 @@
         <v>200</v>
       </c>
       <c r="D13" s="5">
-        <v>100</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+        <v>1000</v>
+      </c>
+      <c r="E13" s="5">
+        <v>4.821726</v>
+      </c>
+      <c r="F13" s="5">
+        <v>4.8276089999999998</v>
+      </c>
+      <c r="G13" s="5">
+        <v>4.8279920000000001</v>
+      </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="5">
@@ -3734,11 +2810,17 @@
         <v>400</v>
       </c>
       <c r="D14" s="5">
-        <v>100</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+        <v>1000</v>
+      </c>
+      <c r="E14" s="5">
+        <v>5.6521369999999997</v>
+      </c>
+      <c r="F14" s="5">
+        <v>5.6502540000000003</v>
+      </c>
+      <c r="G14" s="5">
+        <v>5.654865</v>
+      </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
@@ -3748,11 +2830,17 @@
         <v>800</v>
       </c>
       <c r="D15" s="5">
-        <v>100</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+        <v>1000</v>
+      </c>
+      <c r="E15" s="5">
+        <v>9.9205380000000005</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10.032994</v>
+      </c>
+      <c r="G15" s="5">
+        <v>10.042467</v>
+      </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
@@ -3762,11 +2850,17 @@
         <v>1000</v>
       </c>
       <c r="D16" s="5">
-        <v>100</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+        <v>1000</v>
+      </c>
+      <c r="E16" s="6">
+        <v>10.497</v>
+      </c>
+      <c r="F16" s="6">
+        <v>10.862045</v>
+      </c>
+      <c r="G16" s="6">
+        <v>10.544639</v>
+      </c>
     </row>
     <row r="19" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D19" s="2" t="s">
@@ -3788,9 +2882,9 @@
         <f>AVERAGE(E4:G4)</f>
         <v>1.4521346666666668</v>
       </c>
-      <c r="F20" s="6" t="e">
+      <c r="F20" s="6">
         <f>AVERAGE(E12:G12)</f>
-        <v>#DIV/0!</v>
+        <v>4.8563816666666666</v>
       </c>
     </row>
     <row r="21" spans="4:6" x14ac:dyDescent="0.3">
@@ -3802,9 +2896,9 @@
         <f>AVERAGE(E5:G5)</f>
         <v>5.0433236666666668</v>
       </c>
-      <c r="F21" s="6" t="e">
+      <c r="F21" s="6">
         <f t="shared" ref="F21:F24" si="0">AVERAGE(E13:G13)</f>
-        <v>#DIV/0!</v>
+        <v>4.8257756666666669</v>
       </c>
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.3">
@@ -3816,9 +2910,9 @@
         <f>AVERAGE(E6:G6)</f>
         <v>18.640733999999998</v>
       </c>
-      <c r="F22" s="6" t="e">
+      <c r="F22" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>5.6524186666666667</v>
       </c>
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.3">
@@ -3830,9 +2924,9 @@
         <f>AVERAGE(E7:G7)</f>
         <v>72.271221333333344</v>
       </c>
-      <c r="F23" s="6" t="e">
+      <c r="F23" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>9.9986663333333343</v>
       </c>
     </row>
     <row r="24" spans="4:6" x14ac:dyDescent="0.3">
@@ -3844,9 +2938,9 @@
         <f>AVERAGE(E8:G8)</f>
         <v>100.10557033333333</v>
       </c>
-      <c r="F24" s="6" t="e">
+      <c r="F24" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>10.634561333333334</v>
       </c>
     </row>
   </sheetData>
@@ -3953,17 +3047,17 @@
         <v>1000</v>
       </c>
       <c r="E6" s="6">
-        <v>7.7358529999999996</v>
+        <v>15.015668</v>
       </c>
       <c r="F6" s="6">
-        <v>8.3516139999999996</v>
+        <v>16.922636000000001</v>
       </c>
       <c r="G6" s="6">
-        <v>8.6758369999999996</v>
+        <v>15.103643</v>
       </c>
       <c r="H6" s="6">
         <f t="shared" si="0"/>
-        <v>8.2544346666666666</v>
+        <v>15.680649000000001</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
@@ -3976,12 +3070,18 @@
       <c r="D7" s="5">
         <v>1000</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6" t="e">
+      <c r="E7" s="6">
+        <v>10.497</v>
+      </c>
+      <c r="F7" s="6">
+        <v>10.862045</v>
+      </c>
+      <c r="G7" s="6">
+        <v>10.544639</v>
+      </c>
+      <c r="H7" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>10.634561333333334</v>
       </c>
     </row>
   </sheetData>
@@ -3992,99 +3092,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92881DEB-188C-4DB1-9AD4-F893FE6A3258}">
-  <dimension ref="B3:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="1" t="e">
-        <f>AVERAGE(C4:E4)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="4">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="1" t="e">
-        <f t="shared" ref="F5:F8" si="0">AVERAGE(C5:E5)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="4">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="4">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="4">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB542A8C-C0A9-4DEF-9353-02F1205ED9B2}">
   <dimension ref="B3:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4201,7 +3208,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D9DBD18-7035-4CD6-847F-50448158232D}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/GRÁFICAS.xlsx
+++ b/GRÁFICAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb4d9ba34e02ff95/Escritorio/US/3º/2º CUATRIMESTRE/ASD/TRABAJO-ASD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="224" documentId="8_{224F6AC1-D5D9-4E39-93DA-166DED78EC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1AB9B91-5A40-4C3E-95CD-1EEC933B865B}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="8_{224F6AC1-D5D9-4E39-93DA-166DED78EC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A442F37D-451E-422D-B3FB-65E492B5B53F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7F44F516-FBB9-4CC1-AFE1-16562D403CA9}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Tiempo vs tamaño de la matriz" sheetId="1" r:id="rId1"/>
     <sheet name="Mejora distintas optimizacione " sheetId="5" r:id="rId2"/>
     <sheet name="Speedup (aceleración)" sheetId="3" r:id="rId3"/>
-    <sheet name="Eficiencia" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
   <si>
     <t>Nº de celdas</t>
   </si>
@@ -66,9 +65,6 @@
   </si>
   <si>
     <t>Columnas</t>
-  </si>
-  <si>
-    <t>Hilos</t>
   </si>
   <si>
     <t>Tiempo medio (No Optimizado)</t>
@@ -100,6 +96,33 @@
   <si>
     <t>OPTIMIZADO (OPENMP)</t>
   </si>
+  <si>
+    <t>Tamaño</t>
+  </si>
+  <si>
+    <t>100x100</t>
+  </si>
+  <si>
+    <t>200x200</t>
+  </si>
+  <si>
+    <t>400x400</t>
+  </si>
+  <si>
+    <t>800x800</t>
+  </si>
+  <si>
+    <t>Secuencial</t>
+  </si>
+  <si>
+    <t>Optimizado</t>
+  </si>
+  <si>
+    <t>Speedup</t>
+  </si>
+  <si>
+    <t>Mejora</t>
+  </si>
 </sst>
 </file>
 
@@ -123,13 +146,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,8 +153,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,12 +172,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -182,32 +199,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1057,6 +1074,515 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Mejora y</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-ES" baseline="0"/>
+              <a:t> Speedup con respecto al código secuencial</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Speedup (aceleración)'!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Speedup</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Speedup (aceleración)'!$B$4:$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100x100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200x200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>400x400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>800x800</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000x1000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Speedup (aceleración)'!$E$4:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.29901153212520593</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0449647741400747</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.2981245576786975</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.2278227822782277</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.4128819934179599</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2E88-42C7-81D7-F0DC8A3BF8CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="953952768"/>
+        <c:axId val="953953248"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Speedup (aceleración)'!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mejora</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Speedup (aceleración)'!$B$4:$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100x100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200x200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>400x400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>800x800</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000x1000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Speedup (aceleración)'!$F$4:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-2.3443526170798896</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.3029942494547002E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69679738211469333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.8616457500242144</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.89376261163167037</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2E88-42C7-81D7-F0DC8A3BF8CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="953957088"/>
+        <c:axId val="953956128"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="953952768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="953953248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="953953248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="953952768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="953956128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="953957088"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="953957088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="953956128"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1137,6 +1663,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
   <cs:axisTitle>
@@ -2089,6 +2655,509 @@
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2249,6 +3318,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EBF9CED-AC19-F632-BA64-A863C866968B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB7AF6E0-EA86-01A5-675D-2033840AE6F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2603,342 +3713,342 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="5">
+      <c r="B4" s="2">
         <v>100</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="2">
         <v>100</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="2">
         <v>1000</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>1.6113980000000001</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>1.4158440000000001</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>1.329162</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="5">
+      <c r="B5" s="2">
         <v>200</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="2">
         <v>200</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="2">
         <v>1000</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="3">
         <v>5.0053109999999998</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="3">
         <v>4.5624589999999996</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="3">
         <v>5.562201</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="5">
+      <c r="B6" s="2">
         <v>400</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="2">
         <v>400</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="2">
         <v>1000</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="3">
         <v>19.26736</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="3">
         <v>18.937560000000001</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="3">
         <v>17.717282000000001</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="5">
+      <c r="B7" s="2">
         <v>800</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="2">
         <v>800</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="2">
         <v>1000</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="3">
         <v>71.624598000000006</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="3">
         <v>72.698080000000004</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="3">
         <v>72.490986000000007</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="5">
+      <c r="B8" s="2">
         <v>1000</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="2">
         <v>1000</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="2">
         <v>1000</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="3">
         <v>101.41100900000001</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="3">
         <v>100.48173800000001</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="3">
         <v>98.423963999999998</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="5">
+      <c r="B12" s="2">
         <v>100</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="2">
         <v>100</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="2">
         <v>1000</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="2">
         <v>4.8566950000000002</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="2">
         <v>4.8558019999999997</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="2">
         <v>4.8566479999999999</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="5">
+      <c r="B13" s="2">
         <v>200</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="2">
         <v>200</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="2">
         <v>1000</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="2">
         <v>4.821726</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="2">
         <v>4.8276089999999998</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="2">
         <v>4.8279920000000001</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="5">
+      <c r="B14" s="2">
         <v>400</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="2">
         <v>400</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="2">
         <v>1000</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="2">
         <v>5.6521369999999997</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="2">
         <v>5.6502540000000003</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="2">
         <v>5.654865</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="5">
+      <c r="B15" s="2">
         <v>800</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="2">
         <v>800</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="2">
         <v>1000</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="2">
         <v>9.9205380000000005</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="2">
         <v>10.032994</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="2">
         <v>10.042467</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="5">
+      <c r="B16" s="2">
         <v>1000</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="2">
         <v>1000</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="2">
         <v>1000</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="3">
         <v>10.497</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="3">
         <v>10.862045</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="3">
         <v>10.544639</v>
       </c>
     </row>
     <row r="19" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>12</v>
+      <c r="E19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D20" s="5">
+      <c r="D20" s="2">
         <f>B4*C4</f>
         <v>10000</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="3">
         <f>AVERAGE(E4:G4)</f>
         <v>1.4521346666666668</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="3">
         <f>AVERAGE(E12:G12)</f>
         <v>4.8563816666666666</v>
       </c>
     </row>
     <row r="21" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D21" s="5">
+      <c r="D21" s="2">
         <f>B5*C5</f>
         <v>40000</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="3">
         <f>AVERAGE(E5:G5)</f>
         <v>5.0433236666666668</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="3">
         <f t="shared" ref="F21:F24" si="0">AVERAGE(E13:G13)</f>
         <v>4.8257756666666669</v>
       </c>
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D22" s="5">
+      <c r="D22" s="2">
         <f>B6*C6</f>
         <v>160000</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="3">
         <f>AVERAGE(E6:G6)</f>
         <v>18.640733999999998</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="3">
         <f t="shared" si="0"/>
         <v>5.6524186666666667</v>
       </c>
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D23" s="5">
+      <c r="D23" s="2">
         <f>B7*C7</f>
         <v>640000</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="3">
         <f>AVERAGE(E7:G7)</f>
         <v>72.271221333333344</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="3">
         <f t="shared" si="0"/>
         <v>9.9986663333333343</v>
       </c>
     </row>
     <row r="24" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D24" s="5">
+      <c r="D24" s="2">
         <f>B8*C8</f>
         <v>1000000</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="3">
         <f>AVERAGE(E8:G8)</f>
         <v>100.10557033333333</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="3">
         <f t="shared" si="0"/>
         <v>10.634561333333334</v>
       </c>
@@ -2966,120 +4076,120 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2">
         <v>1000</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>101.41100900000001</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>100.48173800000001</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>98.423963999999998</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <f>AVERAGE(E4:G4)</f>
         <v>100.10557033333333</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2">
         <v>1000</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="3">
         <v>18.777006</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="3">
         <v>19.98086</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="3">
         <v>16.713101999999999</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="3">
         <f t="shared" ref="H5:H7" si="0">AVERAGE(E5:G5)</f>
         <v>18.490322666666668</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2">
         <v>1000</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="3">
         <v>15.015668</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="3">
         <v>16.922636000000001</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="3">
         <v>15.103643</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="3">
         <f t="shared" si="0"/>
         <v>15.680649000000001</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2">
         <v>1000</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="3">
         <v>10.497</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="3">
         <v>10.862045</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="3">
         <v>10.544639</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="3">
         <f t="shared" si="0"/>
         <v>10.634561333333334</v>
       </c>
@@ -3097,122 +4207,119 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>5</v>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="4">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1">
-        <f>AVERAGE(C4:E4)</f>
-        <v>2</v>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1.452</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4.8559999999999999</v>
+      </c>
+      <c r="E4" s="3">
+        <f>C4/D4</f>
+        <v>0.29901153212520593</v>
+      </c>
+      <c r="F4" s="6">
+        <f>((C4-D4)/C4)</f>
+        <v>-2.3443526170798896</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="4">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4">
-        <v>4</v>
-      </c>
-      <c r="D5" s="4">
-        <v>5</v>
-      </c>
-      <c r="E5" s="4">
-        <v>6</v>
-      </c>
-      <c r="F5" s="1">
-        <f t="shared" ref="F5:F8" si="0">AVERAGE(C5:E5)</f>
-        <v>5</v>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5.0430000000000001</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4.8259999999999996</v>
+      </c>
+      <c r="E5" s="3">
+        <f>C5/D5</f>
+        <v>1.0449647741400747</v>
+      </c>
+      <c r="F5" s="6">
+        <f>((C5-D5)/C5)</f>
+        <v>4.3029942494547002E-2</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="4">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4">
-        <v>8</v>
-      </c>
-      <c r="E6" s="4">
-        <v>9</v>
-      </c>
-      <c r="F6" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3">
+        <v>18.640999999999998</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5.6520000000000001</v>
+      </c>
+      <c r="E6" s="3">
+        <f>C6/D6</f>
+        <v>3.2981245576786975</v>
+      </c>
+      <c r="F6" s="6">
+        <f>((C6-D6)/C6)</f>
+        <v>0.69679738211469333</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="4">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4">
-        <v>10</v>
-      </c>
-      <c r="D7" s="4">
-        <v>11</v>
-      </c>
-      <c r="E7" s="4">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3">
+        <v>72.271000000000001</v>
+      </c>
+      <c r="D7" s="2">
+        <v>9.9990000000000006</v>
+      </c>
+      <c r="E7" s="3">
+        <f>C7/D7</f>
+        <v>7.2278227822782277</v>
+      </c>
+      <c r="F7" s="6">
+        <f>((C7-D7)/C7)</f>
+        <v>0.8616457500242144</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="4">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4">
-        <v>13</v>
-      </c>
-      <c r="D8" s="4">
-        <v>14</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="1">
-        <f t="shared" si="0"/>
-        <v>14</v>
+      <c r="C8" s="3">
+        <v>100.10599999999999</v>
+      </c>
+      <c r="D8" s="2">
+        <v>10.635</v>
+      </c>
+      <c r="E8" s="3">
+        <f>C8/D8</f>
+        <v>9.4128819934179599</v>
+      </c>
+      <c r="F8" s="6">
+        <f>((C8-D8)/C8)</f>
+        <v>0.89376261163167037</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D9DBD18-7035-4CD6-847F-50448158232D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/GRÁFICAS.xlsx
+++ b/GRÁFICAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb4d9ba34e02ff95/Escritorio/US/3º/2º CUATRIMESTRE/ASD/TRABAJO-ASD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="8_{224F6AC1-D5D9-4E39-93DA-166DED78EC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A442F37D-451E-422D-B3FB-65E492B5B53F}"/>
+  <xr:revisionPtr revIDLastSave="293" documentId="8_{224F6AC1-D5D9-4E39-93DA-166DED78EC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{726F9E86-3BF4-4E6C-8406-DD445363E69F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7F44F516-FBB9-4CC1-AFE1-16562D403CA9}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
   <si>
     <t>Nº de celdas</t>
   </si>
@@ -123,6 +123,12 @@
   <si>
     <t>Mejora</t>
   </si>
+  <si>
+    <t>OPTIMIZADO (DESENROLLADO)</t>
+  </si>
+  <si>
+    <t>OPTIMIZADO (MPI)</t>
+  </si>
 </sst>
 </file>
 
@@ -203,7 +209,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -215,12 +221,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -865,9 +872,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Mejora distintas optimizacione '!$B$4:$B$7</c:f>
+              <c:f>'Mejora distintas optimizacione '!$B$4:$B$9</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>NO OPTIMIZADO</c:v>
                 </c:pt>
@@ -875,9 +882,15 @@
                   <c:v>OPTIMIZADO (OPENMP)</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>OPTIMIZADO (DESENROLLADO)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OPTIMIZADO (MPI)</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>OPTIMIZADO (OPENMP+DESENRROLLADO)</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>OPTIMIZADO (OPENMP+DESENRROLLADO+MPI)</c:v>
                 </c:pt>
               </c:strCache>
@@ -885,20 +898,20 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Mejora distintas optimizacione '!$H$4:$H$7</c:f>
+              <c:f>'Mejora distintas optimizacione '!$H$4:$H$9</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>100.10557033333333</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>18.490322666666668</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>15.680649000000001</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>10.634561333333334</c:v>
                 </c:pt>
               </c:numCache>
@@ -1502,6 +1515,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="953956128"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -3303,14 +3317,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1615440</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3713,14 +3727,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
@@ -3843,14 +3857,14 @@
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
@@ -4066,7 +4080,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{525178EA-6457-4E02-8C1B-7AB9DF124C34}">
-  <dimension ref="B3:H7"/>
+  <dimension ref="B3:H9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="42.5546875" customWidth="1"/>
@@ -4142,13 +4156,13 @@
         <v>16.713101999999999</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" ref="H5:H7" si="0">AVERAGE(E5:G5)</f>
+        <f t="shared" ref="H5" si="0">AVERAGE(E5:G5)</f>
         <v>18.490322666666668</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>15</v>
@@ -4156,23 +4170,14 @@
       <c r="D6" s="2">
         <v>1000</v>
       </c>
-      <c r="E6" s="3">
-        <v>15.015668</v>
-      </c>
-      <c r="F6" s="3">
-        <v>16.922636000000001</v>
-      </c>
-      <c r="G6" s="3">
-        <v>15.103643</v>
-      </c>
-      <c r="H6" s="3">
-        <f t="shared" si="0"/>
-        <v>15.680649000000001</v>
-      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>15</v>
@@ -4180,17 +4185,56 @@
       <c r="D7" s="2">
         <v>1000</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>15.015668</v>
+      </c>
+      <c r="F8" s="3">
+        <v>16.922636000000001</v>
+      </c>
+      <c r="G8" s="3">
+        <v>15.103643</v>
+      </c>
+      <c r="H8" s="3">
+        <f>AVERAGE(E8:G8)</f>
+        <v>15.680649000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10.497</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F9" s="3">
         <v>10.862045</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G9" s="3">
         <v>10.544639</v>
       </c>
-      <c r="H7" s="3">
-        <f t="shared" si="0"/>
+      <c r="H9" s="3">
+        <f>AVERAGE(E9:G9)</f>
         <v>10.634561333333334</v>
       </c>
     </row>
@@ -4237,7 +4281,7 @@
         <f>C4/D4</f>
         <v>0.29901153212520593</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <f>((C4-D4)/C4)</f>
         <v>-2.3443526170798896</v>
       </c>
@@ -4256,7 +4300,7 @@
         <f>C5/D5</f>
         <v>1.0449647741400747</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <f>((C5-D5)/C5)</f>
         <v>4.3029942494547002E-2</v>
       </c>
@@ -4275,7 +4319,7 @@
         <f>C6/D6</f>
         <v>3.2981245576786975</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <f>((C6-D6)/C6)</f>
         <v>0.69679738211469333</v>
       </c>
@@ -4294,7 +4338,7 @@
         <f>C7/D7</f>
         <v>7.2278227822782277</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <f>((C7-D7)/C7)</f>
         <v>0.8616457500242144</v>
       </c>
@@ -4313,7 +4357,7 @@
         <f>C8/D8</f>
         <v>9.4128819934179599</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <f>((C8-D8)/C8)</f>
         <v>0.89376261163167037</v>
       </c>
